--- a/evaluation_forms/044_team_member_follow_up_evaluation--evaluation_forms.xlsx
+++ b/evaluation_forms/044_team_member_follow_up_evaluation--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1598,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1666,12 +1666,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1683,12 +1683,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1717,12 +1717,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1734,12 +1734,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'hr'}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'HR'}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -1785,12 +1785,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'peer'}</t>
+          <t>peer</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Peer'}</t>
+          <t>Peer</t>
         </is>
       </c>
     </row>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Team Member'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
